--- a/files/九龙-启德-Double Coast I.xlsx
+++ b/files/九龙-启德-Double Coast I.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -146,8 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +220,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,13 +238,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17361,172 +17399,172 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Double Coast I - 3座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>338 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>17 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>321 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1276呎 (4+房)
-$3,152万
+$3152万
 $24,700/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 419呎 (2房)
 $849万
@@ -17534,7 +17572,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 招标单位
@@ -17542,7 +17580,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $977万
@@ -17550,27 +17588,27 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 1260呎 (4+房)
-$2,900万
+$2900万
 $23,016/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $958万
@@ -17578,15 +17616,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,362万
+$1362万
 $21,730/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $832万
@@ -17594,7 +17632,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $996万
@@ -17602,7 +17640,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 463呎 (2房)
 $916万
@@ -17610,7 +17648,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $603万
@@ -17618,7 +17656,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $495万
@@ -17626,7 +17664,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $599万
@@ -17634,7 +17672,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 437呎 (2房)
 $823万
@@ -17642,7 +17680,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 435呎 (2房)
 $815万
@@ -17650,7 +17688,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $590万
@@ -17659,29 +17697,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
-$1,008万
+$1008万
 $22,966/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,394万
+$1394万
 $22,201/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $826万
@@ -17689,7 +17727,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 招标单位
@@ -17697,7 +17735,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $915万
@@ -17705,7 +17743,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $598万
@@ -17713,7 +17751,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $486万
@@ -17721,7 +17759,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $608万
@@ -17729,7 +17767,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $814万
@@ -17737,7 +17775,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $810万
@@ -17745,7 +17783,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $580万
@@ -17754,13 +17792,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -17768,15 +17806,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,404万
+$1404万
 $22,363/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $843万
@@ -17784,7 +17822,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 招标单位
@@ -17792,7 +17830,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $982万
@@ -17800,7 +17838,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $596万
@@ -17808,7 +17846,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $487万
@@ -17816,7 +17854,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $607万
@@ -17824,7 +17862,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $837万
@@ -17832,7 +17870,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $830万
@@ -17840,7 +17878,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $579万
@@ -17849,13 +17887,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -17863,15 +17901,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,387万
+$1387万
 $22,092/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $840万
@@ -17879,7 +17917,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 招标单位
@@ -17887,7 +17925,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $989万
@@ -17895,7 +17933,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $595万
@@ -17903,7 +17941,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $486万
@@ -17911,7 +17949,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $592万
@@ -17919,7 +17957,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $810万
@@ -17927,7 +17965,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $803万
@@ -17935,7 +17973,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $577万
@@ -17944,13 +17982,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -17958,15 +17996,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,384万
+$1384万
 $22,037/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $820万
@@ -17974,15 +18012,15 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
-$1,023万
+$1023万
 $21,453/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $977万
@@ -17990,7 +18028,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $593万
@@ -17998,7 +18036,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $510万
@@ -18006,7 +18044,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $590万
@@ -18014,7 +18052,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $808万
@@ -18022,7 +18060,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $801万
@@ -18030,7 +18068,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $602万
@@ -18039,13 +18077,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -18053,15 +18091,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,365万
+$1365万
 $21,740/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $837万
@@ -18069,7 +18107,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 招标单位
@@ -18077,7 +18115,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $946万
@@ -18085,7 +18123,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $592万
@@ -18093,7 +18131,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $509万
@@ -18101,7 +18139,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $589万
@@ -18109,7 +18147,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $806万
@@ -18117,7 +18155,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $799万
@@ -18125,7 +18163,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $574万
@@ -18134,13 +18172,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -18148,15 +18186,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,377万
+$1377万
 $21,925/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $824万
@@ -18164,15 +18202,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
-$1,008万
+$1008万
 $21,143/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $972万
@@ -18180,7 +18218,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $590万
@@ -18188,7 +18226,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $508万
@@ -18196,7 +18234,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $587万
@@ -18204,7 +18242,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $804万
@@ -18212,7 +18250,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $797万
@@ -18220,7 +18258,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $573万
@@ -18229,13 +18267,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -18243,15 +18281,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,374万
+$1374万
 $21,873/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $822万
@@ -18259,15 +18297,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
-$1,006万
+$1006万
 $21,092/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $942万
@@ -18275,7 +18313,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $589万
@@ -18283,7 +18321,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $478万
@@ -18291,7 +18329,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $586万
@@ -18299,7 +18337,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $803万
@@ -18307,7 +18345,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $795万
@@ -18315,7 +18353,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $571万
@@ -18324,13 +18362,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -18338,15 +18376,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,318万
+$1318万
 $21,016/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $819万
@@ -18354,7 +18392,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $974万
@@ -18362,7 +18400,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $939万
@@ -18370,7 +18408,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $588万
@@ -18378,7 +18416,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $477万
@@ -18386,7 +18424,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $584万
@@ -18394,7 +18432,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $798万
@@ -18402,7 +18440,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $793万
@@ -18410,7 +18448,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $570万
@@ -18419,13 +18457,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -18433,15 +18471,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,429万
+$1429万
 $22,752/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $809万
@@ -18449,7 +18487,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 招标单位
@@ -18457,7 +18495,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $937万
@@ -18465,7 +18503,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $586万
@@ -18473,7 +18511,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $504万
@@ -18481,7 +18519,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $596万
@@ -18489,7 +18527,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $798万
@@ -18497,7 +18535,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $804万
@@ -18505,7 +18543,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $568万
@@ -18514,13 +18552,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $894万
@@ -18528,15 +18566,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,310万
+$1310万
 $20,860/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $808万
@@ -18544,7 +18582,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $967万
@@ -18552,7 +18590,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $923万
@@ -18560,7 +18598,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $583万
@@ -18568,7 +18606,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $468万
@@ -18576,7 +18614,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $580万
@@ -18584,7 +18622,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $794万
@@ -18592,7 +18630,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $785万
@@ -18600,7 +18638,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $566万
@@ -18609,13 +18647,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $892万
@@ -18623,15 +18661,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,305万
+$1305万
 $20,774/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $803万
@@ -18639,7 +18677,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $919万
@@ -18647,7 +18685,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $921万
@@ -18655,7 +18693,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $582万
@@ -18663,7 +18701,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $467万
@@ -18671,7 +18709,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $578万
@@ -18679,7 +18717,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $790万
@@ -18687,7 +18725,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $782万
@@ -18695,7 +18733,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $564万
@@ -18704,13 +18742,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $895万
@@ -18718,15 +18756,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,301万
+$1301万
 $20,723/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $810万
@@ -18734,7 +18772,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $963万
@@ -18742,7 +18780,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $919万
@@ -18750,7 +18788,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $580万
@@ -18758,7 +18796,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $471万
@@ -18766,7 +18804,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $577万
@@ -18774,7 +18812,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $787万
@@ -18782,7 +18820,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $780万
@@ -18790,7 +18828,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $563万
@@ -18799,13 +18837,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -18813,15 +18851,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,298万
+$1298万
 $20,703/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $799万
@@ -18829,7 +18867,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $960万
@@ -18837,7 +18875,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $916万
@@ -18845,7 +18883,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $579万
@@ -18853,7 +18891,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $465万
@@ -18861,7 +18899,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $576万
@@ -18869,7 +18907,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $785万
@@ -18877,7 +18915,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $778万
@@ -18885,7 +18923,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $562万
@@ -18894,13 +18932,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $928万
@@ -18908,15 +18946,15 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,295万
+$1295万
 $20,619/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $797万
@@ -18924,7 +18962,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -18932,7 +18970,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $914万
@@ -18940,7 +18978,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $577万
@@ -18948,7 +18986,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $464万
@@ -18956,7 +18994,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $574万
@@ -18964,7 +19002,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 441呎 (2房)
 $783万
@@ -18972,7 +19010,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $776万
@@ -18980,7 +19018,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $560万
@@ -18989,13 +19027,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $908万
@@ -19003,15 +19041,15 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,292万
+$1292万
 $20,567/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $795万
@@ -19019,7 +19057,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -19027,7 +19065,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $912万
@@ -19035,7 +19073,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $576万
@@ -19043,7 +19081,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $463万
@@ -19051,7 +19089,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $573万
@@ -19059,7 +19097,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $790万
@@ -19067,7 +19105,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $774万
@@ -19075,7 +19113,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $565万
@@ -19084,13 +19122,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $906万
@@ -19098,15 +19136,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,288万
+$1288万
 $20,518/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $793万
@@ -19114,7 +19152,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $943万
@@ -19122,7 +19160,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $890万
@@ -19130,7 +19168,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $574万
@@ -19138,7 +19176,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $462万
@@ -19146,7 +19184,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $571万
@@ -19154,7 +19192,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $780万
@@ -19162,7 +19200,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $781万
@@ -19170,7 +19208,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $557万
@@ -19179,13 +19217,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $904万
@@ -19193,15 +19231,15 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,285万
+$1285万
 $20,498/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $791万
@@ -19209,7 +19247,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $941万
@@ -19217,7 +19255,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $917万
@@ -19225,7 +19263,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $573万
@@ -19233,7 +19271,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $460万
@@ -19241,7 +19279,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $570万
@@ -19249,7 +19287,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 441呎 (2房)
 $778万
@@ -19257,7 +19295,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $770万
@@ -19265,7 +19303,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $556万
@@ -19274,13 +19312,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $901万
@@ -19288,15 +19326,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,297万
+$1297万
 $20,679/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $789万
@@ -19304,7 +19342,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $939万
@@ -19312,7 +19350,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $905万
@@ -19320,7 +19358,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $572万
@@ -19328,7 +19366,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $459万
@@ -19336,7 +19374,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $568万
@@ -19344,7 +19382,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $776万
@@ -19352,7 +19390,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $769万
@@ -19360,7 +19398,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $554万
@@ -19369,13 +19407,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $865万
@@ -19383,15 +19421,15 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,276万
+$1276万
 $20,312/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $786万
@@ -19399,7 +19437,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $898万
@@ -19407,7 +19445,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $867万
@@ -19415,7 +19453,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $569万
@@ -19423,7 +19461,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $457万
@@ -19431,7 +19469,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $566万
@@ -19439,7 +19477,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $772万
@@ -19447,7 +19485,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="K26" s="16" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $765万
@@ -19455,7 +19493,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L26" s="16" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $552万
@@ -19464,13 +19502,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $860万
@@ -19478,15 +19516,15 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,272万
+$1272万
 $20,261/呎
 (25年-07月)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $792万
@@ -19494,7 +19532,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $916万
@@ -19502,7 +19540,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $864万
@@ -19510,7 +19548,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $567万
@@ -19518,7 +19556,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $456万
@@ -19526,7 +19564,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $564万
@@ -19534,7 +19572,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $778万
@@ -19542,7 +19580,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $763万
@@ -19550,7 +19588,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L27" s="16" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $550万
@@ -19559,13 +19597,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $892万
@@ -19573,15 +19611,15 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,269万
+$1269万
 $20,212/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $782万
@@ -19589,7 +19627,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -19597,7 +19635,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $870万
@@ -19605,7 +19643,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $572万
@@ -19613,7 +19651,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $455万
@@ -19621,7 +19659,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $563万
@@ -19629,7 +19667,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 441呎 (2房)
 $768万
@@ -19637,7 +19675,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="K28" s="16" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $761万
@@ -19645,7 +19683,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L28" s="16" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $549万
@@ -19654,13 +19692,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $866万
@@ -19668,15 +19706,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,266万
+$1266万
 $20,161/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $780万
@@ -19684,7 +19722,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $936万
@@ -19692,7 +19730,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $879万
@@ -19700,7 +19738,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $564万
@@ -19708,7 +19746,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $454万
@@ -19716,7 +19754,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $561万
@@ -19724,7 +19762,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $766万
@@ -19732,7 +19770,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K29" s="16" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $768万
@@ -19740,7 +19778,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="L29" s="16" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $548万
@@ -19749,13 +19787,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $863万
@@ -19763,15 +19801,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,263万
+$1263万
 $20,142/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $778万
@@ -19779,7 +19817,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $890万
@@ -19787,7 +19825,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $857万
@@ -19795,7 +19833,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $563万
@@ -19803,7 +19841,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $452万
@@ -19811,7 +19849,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $560万
@@ -19819,7 +19857,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $764万
@@ -19827,7 +19865,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="K30" s="16" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $757万
@@ -19835,7 +19873,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L30" s="16" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $546万
@@ -19844,13 +19882,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 招标单位
@@ -19858,15 +19896,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,260万
+$1260万
 $20,094/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $776万
@@ -19874,7 +19912,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $922万
@@ -19882,7 +19920,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $855万
@@ -19890,7 +19928,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $587万
@@ -19898,7 +19936,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $451万
@@ -19906,7 +19944,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $559万
@@ -19914,7 +19952,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $762万
@@ -19922,7 +19960,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="K31" s="16" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $755万
@@ -19930,7 +19968,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="L31" s="16" t="inlineStr">
+      <c r="L30" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $570万
@@ -19939,13 +19977,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $899万
@@ -19953,15 +19991,15 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 627呎 (3房)
-$1,242万
+$1242万
 $19,802/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $774万
@@ -19969,7 +20007,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $930万
@@ -19977,7 +20015,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $863万
@@ -19985,7 +20023,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $586万
@@ -19993,7 +20031,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $450万
@@ -20001,7 +20039,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $557万
@@ -20009,7 +20047,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $760万
@@ -20017,7 +20055,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="K32" s="16" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $753万
@@ -20025,7 +20063,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="L32" s="16" t="inlineStr">
+      <c r="L31" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $544万
@@ -20034,13 +20072,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 439呎 (2房)
 $885万
@@ -20048,15 +20086,15 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 628呎 (3房)
-$1,258万
+$1258万
 $20,040/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 420呎 (2房)
 $781万
@@ -20064,7 +20102,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -20072,7 +20110,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $866万
@@ -20080,7 +20118,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $584万
@@ -20088,7 +20126,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $449万
@@ -20096,7 +20134,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $556万
@@ -20104,7 +20142,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>J | 440呎 (2房)
 $767万
@@ -20112,7 +20150,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="K33" s="16" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>K | 437呎 (2房)
 $760万
@@ -20120,7 +20158,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="L33" s="16" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>L | 320呎 (1房)
 $548万
@@ -20129,16 +20167,16 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr"/>
-      <c r="D34" s="17" t="inlineStr"/>
-      <c r="E34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr"/>
+      <c r="C33" s="21" t="inlineStr"/>
+      <c r="D33" s="21" t="inlineStr"/>
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 480呎 (2房)
 $927万
@@ -20146,7 +20184,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $847万
@@ -20154,7 +20192,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $578万
@@ -20162,7 +20200,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $444万
@@ -20170,7 +20208,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $550万
@@ -20178,7 +20216,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>J | 446呎 (2房)
 $758万
@@ -20186,19 +20224,19 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="K34" s="17" t="inlineStr"/>
-      <c r="L34" s="17" t="inlineStr"/>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr"/>
-      <c r="C35" s="17" t="inlineStr"/>
-      <c r="D35" s="17" t="inlineStr"/>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="K33" s="21" t="inlineStr"/>
+      <c r="L33" s="21" t="inlineStr"/>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr"/>
+      <c r="C34" s="21" t="inlineStr"/>
+      <c r="D34" s="21" t="inlineStr"/>
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 480呎 (2房)
 $917万
@@ -20206,7 +20244,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $859万
@@ -20214,7 +20252,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $577万
@@ -20222,7 +20260,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $443万
@@ -20230,7 +20268,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $549万
@@ -20238,7 +20276,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>J | 446呎 (2房)
 $756万
@@ -20246,19 +20284,19 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="K35" s="17" t="inlineStr"/>
-      <c r="L35" s="17" t="inlineStr"/>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr"/>
-      <c r="C36" s="17" t="inlineStr"/>
-      <c r="D36" s="17" t="inlineStr"/>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr"/>
+      <c r="L34" s="21" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr"/>
+      <c r="C35" s="21" t="inlineStr"/>
+      <c r="D35" s="21" t="inlineStr"/>
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 480呎 (2房)
 $923万
@@ -20266,7 +20304,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 462呎 (2房)
 $876万
@@ -20274,7 +20312,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $576万
@@ -20282,7 +20320,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $442万
@@ -20290,7 +20328,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $548万
@@ -20298,7 +20336,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
         <is>
           <t>J | 446呎 (2房)
 $780万
@@ -20306,19 +20344,19 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="K36" s="17" t="inlineStr"/>
-      <c r="L36" s="17" t="inlineStr"/>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr"/>
-      <c r="C37" s="17" t="inlineStr"/>
-      <c r="D37" s="17" t="inlineStr"/>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="K35" s="21" t="inlineStr"/>
+      <c r="L35" s="21" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr"/>
+      <c r="C36" s="21" t="inlineStr"/>
+      <c r="D36" s="21" t="inlineStr"/>
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>D | 480呎 (2房)
 $921万
@@ -20326,7 +20364,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>E | 336呎 (1房)
 $610万
@@ -20334,7 +20372,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>F | 325呎 (1房)
 $568万
@@ -20342,7 +20380,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $437万
@@ -20350,7 +20388,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $541万
@@ -20358,7 +20396,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
         <is>
           <t>J | 446呎 (2房)
 $770万
@@ -20366,19 +20404,19 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="K37" s="17" t="inlineStr"/>
-      <c r="L37" s="17" t="inlineStr"/>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr"/>
-      <c r="C38" s="17" t="inlineStr"/>
-      <c r="D38" s="17" t="inlineStr"/>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="K36" s="21" t="inlineStr"/>
+      <c r="L36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr"/>
+      <c r="C37" s="21" t="inlineStr"/>
+      <c r="D37" s="21" t="inlineStr"/>
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>D | 480呎 (2房)
 $919万
@@ -20386,7 +20424,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>E | 336呎 (1房)
 $609万
@@ -20394,7 +20432,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>F | 326呎 (1房)
 $535万
@@ -20402,7 +20440,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $427万
@@ -20410,7 +20448,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I38" s="16" t="inlineStr">
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $541万
@@ -20418,7 +20456,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="J37" s="20" t="inlineStr">
         <is>
           <t>J | 446呎 (2房)
 $728万
@@ -20426,19 +20464,19 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="K38" s="17" t="inlineStr"/>
-      <c r="L38" s="17" t="inlineStr"/>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr"/>
-      <c r="D39" s="17" t="inlineStr"/>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr"/>
+      <c r="L37" s="21" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr"/>
+      <c r="D38" s="21" t="inlineStr"/>
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 480呎 (2房)
 招标单位
@@ -20446,7 +20484,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>E | 297呎 (1房)
 $632万
@@ -20454,7 +20492,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>F | 327呎 (1房)
 $538万
@@ -20462,7 +20500,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>G | 265呎 (开放式)
 $422万
@@ -20470,7 +20508,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I39" s="16" t="inlineStr">
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>H | 324呎 (1房)
 $541万
@@ -20478,7 +20516,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J39" s="16" t="inlineStr">
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>J | 446呎 (2房)
 $720万
@@ -20486,12 +20524,12 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="K39" s="17" t="inlineStr"/>
-      <c r="L39" s="17" t="inlineStr"/>
+      <c r="K38" s="21" t="inlineStr"/>
+      <c r="L38" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -20504,127 +20542,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Double Coast I - 5座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 426呎 (2房)
 $953万
@@ -20632,32 +20670,32 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 437呎 (2房)
-$1,000万
+$1000万
 $22,883/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 609呎 (3房)
-$1,628万
+$1628万
 $26,732/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 427呎 (2房)
 $816万
@@ -20665,7 +20703,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
 $871万
@@ -20673,7 +20711,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $620万
@@ -20681,7 +20719,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 304呎 (1房)
 $620万
@@ -20689,7 +20727,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 439呎 (2房)
 $902万
@@ -20698,13 +20736,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 427呎 (2房)
 $811万
@@ -20712,7 +20750,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
 $866万
@@ -20720,7 +20758,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $616万
@@ -20728,7 +20766,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 304呎 (1房)
 $616万
@@ -20736,7 +20774,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 439呎 (2房)
 $897万
@@ -20745,13 +20783,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 427呎 (2房)
 $807万
@@ -20759,7 +20797,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 436呎 (2房)
 $861万
@@ -20767,7 +20805,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $612万
@@ -20775,7 +20813,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 305呎 (1房)
 $612万
@@ -20783,7 +20821,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 439呎 (2房)
 $892万
@@ -20792,13 +20830,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 390呎 (2房)
 $850万
@@ -20806,15 +20844,15 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 398呎 (2房)
-$1,020万
+$1020万
 $25,628/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 267呎 (1房)
 $640万
@@ -20822,7 +20860,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 267呎 (1房)
 $662万
@@ -20830,10 +20868,10 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 445呎 (2房)
-$1,135万
+$1135万
 $25,506/呎
 (24年-11月)</t>
         </is>
